--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6996254-3FC0-4C99-A6C2-6794154B53E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB98220D-77E8-4B11-A6F9-289119C5F393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33300" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5565" yWindow="840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2069,7 +2069,7 @@
         <v>173</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
         <v>175</v>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB98220D-77E8-4B11-A6F9-289119C5F393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0778DA6C-E89B-4101-AC5F-1A64F4806580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5565" yWindow="840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="3945" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="263">
   <si>
     <t>SKU</t>
   </si>
@@ -800,6 +800,15 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£15.17</t>
+  </si>
+  <si>
+    <t>£18.31</t>
+  </si>
+  <si>
+    <t>£56.17</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1280,7 @@
         <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="R2" t="s">
         <v>31</v>
@@ -1327,7 +1336,7 @@
         <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="R3" t="s">
         <v>41</v>
@@ -1943,7 +1952,7 @@
         <v>30</v>
       </c>
       <c r="Q14" t="s">
-        <v>30</v>
+        <v>262</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
